--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_177_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_177_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8403</v>
+        <v>4.7401</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0803</v>
+        <v>3.3162</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7599</v>
+        <v>1.4239</v>
       </c>
       <c r="G2" t="n">
         <v>3.4029</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9709</v>
+        <v>0.8707</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1766</v>
+        <v>0.0593</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1475</v>
+        <v>0.8114</v>
       </c>
       <c r="V2" t="n">
         <v>0.9304</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6222</v>
+        <v>2.9659</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0795</v>
+        <v>2.7257</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5427</v>
+        <v>0.2402</v>
       </c>
       <c r="G3" t="n">
         <v>0.1027</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6302</v>
+        <v>0.9739</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4604</v>
+        <v>0.1065</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1699</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.9615</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6842</v>
+        <v>2.5417</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7158</v>
+        <v>3.7503</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0316</v>
+        <v>-1.2086</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6955</v>
+        <v>2.5195</v>
       </c>
       <c r="H4" t="n">
-        <v>0.053</v>
+        <v>3.1317</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6425</v>
+        <v>-0.6122</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7613</v>
+        <v>4.2454</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9579</v>
+        <v>2.8001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8034</v>
+        <v>1.4453</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0659</v>
+        <v>-1.7259</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9049</v>
+        <v>0.3317</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1609</v>
+        <v>-2.0576</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3651</v>
+        <v>0.5168</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0455</v>
+        <v>-0.2867</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4106</v>
+        <v>0.8035</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>3.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.4306</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4398</v>
+        <v>1.6758</v>
       </c>
       <c r="E5" t="n">
-        <v>2.85</v>
+        <v>2.1443</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4102</v>
+        <v>-0.4685</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5195</v>
+        <v>0.6955</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1317</v>
+        <v>0.053</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6122</v>
+        <v>0.6425</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2454</v>
+        <v>2.7613</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8001</v>
+        <v>0.9579</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4453</v>
+        <v>1.8034</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7259</v>
+        <v>-2.0659</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3317</v>
+        <v>-0.9049</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0576</v>
+        <v>-1.1609</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.7112</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5851</v>
+        <v>0.3567</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.187</v>
+        <v>-0.617</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6019</v>
+        <v>0.9737</v>
       </c>
       <c r="V5" t="n">
-        <v>3.2166</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>4.4306</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4348</v>
+        <v>1.0706</v>
       </c>
       <c r="E6" t="n">
-        <v>2.157</v>
+        <v>0.2487</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7222</v>
+        <v>0.8218</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6479</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2531</v>
+        <v>0.6903</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.9009</v>
+        <v>-0.1706</v>
       </c>
       <c r="J6" t="n">
-        <v>0.096</v>
+        <v>0.7557</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2036</v>
+        <v>0.6085</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1077</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7438</v>
+        <v>-0.236</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0495</v>
+        <v>0.0818</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7933</v>
+        <v>-0.3178</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0801</v>
+        <v>0.1386</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4708</v>
+        <v>-0.507</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6093</v>
+        <v>0.6456</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4665</v>
+        <v>-0.2836</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2836</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3743</v>
+        <v>0.3307</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7205</v>
+        <v>1.2881</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6538</v>
+        <v>-0.9574</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5197000000000001</v>
+        <v>-1.6479</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6903</v>
+        <v>1.2531</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1706</v>
+        <v>-2.9009</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7557</v>
+        <v>0.096</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6085</v>
+        <v>1.2036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>-1.1077</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.236</v>
+        <v>-1.7438</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0818</v>
+        <v>0.0495</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3178</v>
+        <v>-1.7933</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4424</v>
+        <v>0.9759</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0351</v>
+        <v>0.6018</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4775</v>
+        <v>0.3741</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2836</v>
+        <v>1.4665</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X7" t="n">
         <v>-0.2836</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.658</v>
+        <v>-0.1129</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0573</v>
+        <v>1.1319</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7153</v>
+        <v>-1.2448</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6062</v>
@@ -1078,13 +1078,13 @@
         <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2838</v>
+        <v>0.2614</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1019</v>
+        <v>-0.0272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1819</v>
+        <v>0.2886</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9609</v>
+        <v>-2.5233</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9099</v>
+        <v>-0.674</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.051</v>
+        <v>-1.8494</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7298</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1589</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2627</v>
+        <v>-0.0611</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4007</v>
+        <v>-3.9392</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1518</v>
+        <v>-1.9591</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2489</v>
+        <v>-1.9801</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2169</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8074</v>
+        <v>-0.3459</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.5542</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0606</v>
+        <v>0.2082</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.376000000000002</v>
+        <v>6.749400000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>11.5987</v>
+        <v>11.9721</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.2228</v>
+        <v>-5.2229</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9605000000000006</v>
@@ -1312,13 +1312,13 @@
         <v>6.9588</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6535</v>
+        <v>3.0268</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2579</v>
+        <v>-1.8848</v>
       </c>
       <c r="U11" t="n">
-        <v>4.9115</v>
+        <v>4.9114</v>
       </c>
       <c r="V11" t="n">
         <v>4.6831</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4327</v>
+        <v>2.0954</v>
       </c>
       <c r="E12" t="n">
-        <v>4.3243</v>
+        <v>3.8525</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8916</v>
+        <v>-1.7571</v>
       </c>
       <c r="G12" t="n">
         <v>1.3939</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.5623</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3778</v>
+        <v>-0.094</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5219</v>
+        <v>0.6563</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7886</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0555</v>
+        <v>0.4094</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1404</v>
+        <v>0.4942</v>
       </c>
       <c r="F13" t="n">
         <v>-0.0848</v>
@@ -1468,10 +1468,10 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1652</v>
+        <v>0.1887</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U13" t="n">
         <v>0.4323</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2807</v>
+        <v>-0.4988</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3185</v>
+        <v>1.7334</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5992</v>
+        <v>-2.2322</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6247</v>
+        <v>0.4699</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5679</v>
+        <v>-1.4573</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0568</v>
+        <v>1.9272</v>
       </c>
       <c r="J14" t="n">
-        <v>0.276</v>
+        <v>2.2112</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4601</v>
+        <v>-0.1408</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7361</v>
+        <v>2.352</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-1.7413</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1078</v>
+        <v>-1.3165</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7929</v>
+        <v>-0.4248</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1199</v>
+        <v>-1.2186</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1019</v>
+        <v>-1.0139</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.018</v>
+        <v>-0.2047</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4538</v>
+        <v>-0.7633</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2347</v>
+        <v>1.8467</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2191</v>
+        <v>-2.6099</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8643</v>
+        <v>-0.6247</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.132</v>
+        <v>-0.5679</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2677</v>
+        <v>-0.0568</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2803</v>
+        <v>0.276</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6582</v>
+        <v>-0.4601</v>
       </c>
       <c r="L15" t="n">
-        <v>0.378</v>
+        <v>0.7361</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5841</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4738</v>
+        <v>-0.1078</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1103</v>
+        <v>-0.7929</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3369</v>
+        <v>-0.6025</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7741</v>
+        <v>-0.5737</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4371</v>
+        <v>-0.0288</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8197</v>
+        <v>2.1444</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0523</v>
+        <v>-0.7842</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9111</v>
+        <v>-0.3526</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9635</v>
+        <v>-0.4315</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9415</v>
+        <v>-1.8643</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8584</v>
+        <v>-2.132</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9169</v>
+        <v>0.2677</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5459000000000001</v>
+        <v>-0.2803</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7423</v>
+        <v>-0.6582</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2882</v>
+        <v>0.378</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4874</v>
+        <v>-1.5841</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1161</v>
+        <v>-1.4738</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3713</v>
+        <v>-0.1103</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2113</v>
+        <v>-0.6673</v>
       </c>
       <c r="T16" t="n">
-        <v>0.311</v>
+        <v>-0.892</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0997</v>
+        <v>0.2247</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>0.8197</v>
       </c>
       <c r="W16" t="n">
-        <v>1.214</v>
+        <v>0.8197</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3967</v>
+        <v>-1.1541</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2616</v>
+        <v>-0.5998</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6583</v>
+        <v>-0.5543</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4699</v>
+        <v>-0.2581</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4573</v>
+        <v>0.448</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9272</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2112</v>
+        <v>1.2434</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1408</v>
+        <v>1.2604</v>
       </c>
       <c r="L17" t="n">
-        <v>2.352</v>
+        <v>-0.017</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7413</v>
+        <v>-1.5015</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3165</v>
+        <v>-0.8123</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4248</v>
+        <v>-0.6891</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1165</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4857</v>
+        <v>-0.8252</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6308</v>
+        <v>0.0193</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4234</v>
+        <v>-1.1862</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6857</v>
+        <v>-0.978</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2623</v>
+        <v>-0.2082</v>
       </c>
       <c r="G18" t="n">
         <v>1.8372</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4173</v>
+        <v>0.6546</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.411</v>
+        <v>-0.7033</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8284</v>
+        <v>1.3579</v>
       </c>
       <c r="V18" t="n">
         <v>-2.2862</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5967</v>
+        <v>-1.5692</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4818</v>
+        <v>0.2034</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1149</v>
+        <v>-1.7726</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2581</v>
+        <v>-0.9415</v>
       </c>
       <c r="H19" t="n">
-        <v>0.448</v>
+        <v>-1.8584</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7060999999999999</v>
+        <v>0.9169</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2434</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2604</v>
+        <v>-0.7423</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.017</v>
+        <v>1.2882</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5015</v>
+        <v>-1.4874</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8123</v>
+        <v>-1.1161</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6891</v>
+        <v>-0.3713</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2485</v>
+        <v>-0.3055</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7073</v>
+        <v>-0.3967</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5412</v>
+        <v>0.0912</v>
       </c>
       <c r="V19" t="n">
         <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6607</v>
+        <v>-2.1388</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3309</v>
+        <v>-0.9771</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3297</v>
+        <v>-1.1617</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0201</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1946</v>
+        <v>0.3273</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3282</v>
+        <v>0.4962</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7501</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.376099999999999</v>
+        <v>-5.589799999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>5.222799999999999</v>
+        <v>5.2227</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.5988</v>
+        <v>-10.8123</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9604999999999999</v>
+        <v>0.9605000000000001</v>
       </c>
       <c r="H21" t="n">
         <v>-6.668200000000001</v>
@@ -2068,7 +2068,7 @@
         <v>10.7393</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1838000000000001</v>
+        <v>0.1838000000000002</v>
       </c>
       <c r="L21" t="n">
         <v>10.5554</v>
@@ -2077,7 +2077,7 @@
         <v>-9.7789</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.851999999999999</v>
+        <v>-6.852000000000001</v>
       </c>
       <c r="O21" t="n">
         <v>-2.9268</v>
@@ -2092,13 +2092,13 @@
         <v>6.9586</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.653299999999999</v>
+        <v>-1.8669</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.9115</v>
+        <v>-4.9113</v>
       </c>
       <c r="U21" t="n">
-        <v>2.2582</v>
+        <v>3.0444</v>
       </c>
       <c r="V21" t="n">
         <v>-4.6831</v>
